--- a/artfynd/A 60620-2025 artfynd.xlsx
+++ b/artfynd/A 60620-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80685796</v>
+        <v>121146952</v>
       </c>
       <c r="B2" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storåsen, Jmt</t>
+          <t>Vontjärnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555313.1025391137</v>
+        <v>555501</v>
       </c>
       <c r="R2" t="n">
-        <v>6973391.091388138</v>
+        <v>6973289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80685797</v>
+        <v>80685795</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555315.842978945</v>
+        <v>555382</v>
       </c>
       <c r="R3" t="n">
-        <v>6973391.137707087</v>
+        <v>6973456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80685825</v>
+        <v>80685799</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555336.812730705</v>
+        <v>555323</v>
       </c>
       <c r="R4" t="n">
-        <v>6973366.855602168</v>
+        <v>6973378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +966,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80685794</v>
+        <v>80685825</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555355.9836520811</v>
+        <v>555337</v>
       </c>
       <c r="R5" t="n">
-        <v>6973421.927595651</v>
+        <v>6973367</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80685829</v>
+        <v>121146951</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storåsen, Jmt</t>
+          <t>Vontjärnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555355.116468961</v>
+        <v>555336</v>
       </c>
       <c r="R6" t="n">
-        <v>6973419.175560028</v>
+        <v>6973451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80685799</v>
+        <v>80685797</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555322.9176739153</v>
+        <v>555316</v>
       </c>
       <c r="R7" t="n">
-        <v>6973378.026545393</v>
+        <v>6973391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80685795</v>
+        <v>80685829</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555381.903152129</v>
+        <v>555355</v>
       </c>
       <c r="R8" t="n">
-        <v>6973456.12680722</v>
+        <v>6973419</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80685827</v>
+        <v>121146954</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storåsen, Jmt</t>
+          <t>Vontjärnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555338.0998391047</v>
+        <v>555305</v>
       </c>
       <c r="R9" t="n">
-        <v>6973398.813679275</v>
+        <v>6973374</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80685828</v>
+        <v>121146960</v>
       </c>
       <c r="B10" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storåsen, Jmt</t>
+          <t>Vontjärnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555342.8137747048</v>
+        <v>555313</v>
       </c>
       <c r="R10" t="n">
-        <v>6973390.224994416</v>
+        <v>6973435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-10-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1686,12 +1551,7 @@
         <v>121146948</v>
       </c>
       <c r="B11" t="n">
-        <v>79717</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121146951</v>
+        <v>121146953</v>
       </c>
       <c r="B12" t="n">
-        <v>74713</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555336</v>
+        <v>555311</v>
       </c>
       <c r="R12" t="n">
-        <v>6973451</v>
+        <v>6973435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,50 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121146952</v>
+        <v>80685794</v>
       </c>
       <c r="B13" t="n">
-        <v>95645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vontjärnåsen, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555501</v>
+        <v>555356</v>
       </c>
       <c r="R13" t="n">
-        <v>6973289</v>
+        <v>6973422</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,12 +1827,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1992,12 +1842,7 @@
         <v>121146956</v>
       </c>
       <c r="B14" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121146953</v>
+        <v>80685796</v>
       </c>
       <c r="B15" t="n">
-        <v>79717</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vontjärnåsen, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555311</v>
+        <v>555313</v>
       </c>
       <c r="R15" t="n">
-        <v>6973435</v>
+        <v>6973391</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,27 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121146954</v>
+        <v>80685828</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vontjärnåsen, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555305</v>
+        <v>555343</v>
       </c>
       <c r="R16" t="n">
-        <v>6973374</v>
+        <v>6973390</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,27 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121146960</v>
+        <v>80685798</v>
       </c>
       <c r="B17" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,34 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vontjärnåsen, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555313</v>
+        <v>555275</v>
       </c>
       <c r="R17" t="n">
-        <v>6973435</v>
+        <v>6973406</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2019-10-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,15 +2215,112 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>80685827</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555338</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6973399</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-10-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-10-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
